--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$27]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[EditionVisual!$B$2:$F$9]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$E$42]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[Transition!$B$2:$J$13]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[Transition!$B$2:$J$15]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[CardSet!$B$2:$I$21]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1"><![CDATA[CardSetSuit!$B$2:$D$72]]></definedName>
   </definedNames>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="331">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -54,25 +54,25 @@
     <t xml:space="preserve">int</t>
   </si>
   <si>
-    <t xml:space="preserve">득점 카드 하나의 연출 길이</t>
+    <t xml:space="preserve">득점 카드 하나의 연출 길이. 값 하나를 읽고 다음 것이 옵니다</t>
   </si>
   <si>
     <t xml:space="preserve">JokerStepMs</t>
   </si>
   <si>
-    <t xml:space="preserve">조커 하나의 연출 길이</t>
+    <t xml:space="preserve">조커 하나의 연출 길이. 눈이 판에서 조커 줄로 옮겨 가는 몫이 더 듭니다</t>
   </si>
   <si>
     <t xml:space="preserve">RetriggerStepMs</t>
   </si>
   <si>
-    <t xml:space="preserve">재발동의 연출 길이</t>
+    <t xml:space="preserve">재발동의 연출 길이. 같은 카드가 한 번 더 세는 것이 보여야 합니다</t>
   </si>
   <si>
     <t xml:space="preserve">HandLabelMs</t>
   </si>
   <si>
-    <t xml:space="preserve">족보 표시의 길이</t>
+    <t xml:space="preserve">족보 표시의 길이. 족보를 읽고 나서 세기 시작합니다</t>
   </si>
   <si>
     <t xml:space="preserve">MultiplyMs</t>
@@ -733,6 +733,18 @@
   </si>
   <si>
     <t xml:space="preserve">전환을 줄였을 때. **0이 아닙니다** — 갈아 끼우는 프레임은 어느 설정에서도 보이면 안 됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title_screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">타이틀에서 전면 화면(시작 · 콜렉션 · 리더보드)으로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">screen_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전면 화면에서 타이틀로</t>
   </si>
   <si>
     <t xml:space="preserve">:table CardSet(key=set_id)</t>
@@ -1212,7 +1224,7 @@
     <col min="2" max="2" width="41.015625" customWidth="1"/>
     <col min="3" max="3" width="7.03125" customWidth="1"/>
     <col min="4" max="4" width="10.546875" customWidth="1"/>
-    <col min="5" max="5" width="46.875" customWidth="1"/>
+    <col min="5" max="5" width="50.390625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1251,7 +1263,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>230</v>
+        <v>420</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>9</v>
@@ -1265,7 +1277,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="6">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>11</v>
@@ -1279,7 +1291,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="5">
-        <v>170</v>
+        <v>320</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>13</v>
@@ -1293,7 +1305,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="6">
-        <v>420</v>
+        <v>620</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>15</v>
@@ -2389,7 +2401,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.53125" customWidth="1"/>
@@ -2775,8 +2787,66 @@
         <v>235</v>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D14" s="6">
+        <v>390</v>
+      </c>
+      <c r="E14" s="6">
+        <v>50</v>
+      </c>
+      <c r="F14" s="6">
+        <v>360</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D15" s="5">
+        <v>390</v>
+      </c>
+      <c r="E15" s="5">
+        <v>50</v>
+      </c>
+      <c r="F15" s="5">
+        <v>360</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:J13"/>
+  <autoFilter ref="B2:J15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2799,10 +2869,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2817,28 +2887,28 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3">
@@ -2849,10 +2919,10 @@
         <v>91</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>201</v>
@@ -2867,7 +2937,7 @@
         <v>200</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4">
@@ -2878,48 +2948,48 @@
         <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>100</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>214</v>
@@ -2927,10 +2997,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
@@ -2945,7 +3015,7 @@
         <v>107</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>214</v>
@@ -2953,10 +3023,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D7" s="5">
         <v>3</v>
@@ -2971,7 +3041,7 @@
         <v>107</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>214</v>
@@ -2979,16 +3049,16 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D8" s="6">
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>214</v>
@@ -2997,7 +3067,7 @@
         <v>107</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>214</v>
@@ -3005,16 +3075,16 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>214</v>
@@ -3023,7 +3093,7 @@
         <v>107</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>214</v>
@@ -3031,16 +3101,16 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D10" s="6">
         <v>6</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>214</v>
@@ -3049,24 +3119,24 @@
         <v>107</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>214</v>
@@ -3075,24 +3145,24 @@
         <v>107</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D12" s="6">
         <v>8</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>214</v>
@@ -3101,24 +3171,24 @@
         <v>107</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D13" s="5">
         <v>9</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>214</v>
@@ -3127,24 +3197,24 @@
         <v>107</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D14" s="6">
         <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>214</v>
@@ -3153,7 +3223,7 @@
         <v>107</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>214</v>
@@ -3161,16 +3231,16 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D15" s="5">
         <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>214</v>
@@ -3179,7 +3249,7 @@
         <v>107</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>214</v>
@@ -3187,16 +3257,16 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D16" s="6">
         <v>12</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>214</v>
@@ -3205,7 +3275,7 @@
         <v>107</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>214</v>
@@ -3213,16 +3283,16 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D17" s="5">
         <v>13</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>214</v>
@@ -3231,7 +3301,7 @@
         <v>107</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>214</v>
@@ -3239,16 +3309,16 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D18" s="6">
         <v>14</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>214</v>
@@ -3257,7 +3327,7 @@
         <v>107</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>214</v>
@@ -3265,16 +3335,16 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D19" s="5">
         <v>15</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>214</v>
@@ -3283,7 +3353,7 @@
         <v>107</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>214</v>
@@ -3291,16 +3361,16 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D20" s="6">
         <v>16</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>214</v>
@@ -3309,24 +3379,24 @@
         <v>107</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D21" s="5">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>214</v>
@@ -3335,10 +3405,10 @@
         <v>107</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -3360,10 +3430,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3373,10 +3443,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>194</v>
@@ -3387,10 +3457,10 @@
         <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>200</v>
@@ -3401,761 +3471,761 @@
         <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="5" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="5" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
